--- a/dividends/shares_mapping.xlsx
+++ b/dividends/shares_mapping.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8390"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
